--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-05-2025.xlsx
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>£46.74</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£45.75</t>
+          <t>£41.59</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£50.05</t>
+          <t>£45.51</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>£48.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£50.42</t>
+          <t>£45.85</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£768.0</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£785.69</t>
+          <t>£714.40</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>£1,037.63</t>
+          <t>£943.20</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£40.62</t>
+          <t>£36.92</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£48.65</t>
+          <t>£44.24</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£57.57</t>
+          <t>£52.35</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£61.03</t>
+          <t>£55.49</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£48.95</t>
+          <t>£44.53</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£46.80</t>
+          <t>£42.56</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>£48.15</t>
+          <t>£43.78</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1,256.49</t>
+          <t>£1,142.11</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1,338.05</t>
+          <t>£1,216.37</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>£1,302.81</t>
+          <t>£1,184.38</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
